--- a/FINAL_REVIEW1-NUMBERS/FINALNUMBERS.xlsx
+++ b/FINAL_REVIEW1-NUMBERS/FINALNUMBERS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Prajwal Anand\Desktop\sem7_project\active_BIBINPROJECT\FINAL_REVIEW1-NUMBERS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B753C73-AA2C-4F6A-A250-A7D103798AA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEF33D31-6E20-49A4-8C20-45771AC498C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -51,7 +51,7 @@
     <t>constant : pi * 0.2m</t>
   </si>
   <si>
-    <t>B: breadth design</t>
+    <t>B: compressor blade breadth ,design</t>
   </si>
 </sst>
 </file>
@@ -87,13 +87,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -124,7 +127,7 @@
     <xdr:to>
       <xdr:col>18</xdr:col>
       <xdr:colOff>199386</xdr:colOff>
-      <xdr:row>24</xdr:row>
+      <xdr:row>23</xdr:row>
       <xdr:rowOff>122609</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -161,15 +164,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
+      <xdr:colOff>15240</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>175260</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>1143059</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>116865</xdr:rowOff>
+      <xdr:colOff>1158299</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>109245</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -192,7 +195,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3992880" y="914400"/>
+          <a:off x="4008120" y="1272540"/>
           <a:ext cx="1143059" cy="482625"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -471,46 +474,46 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15" style="2" customWidth="1"/>
-    <col min="2" max="2" width="11.21875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="14.33203125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="15" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.21875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="17.6640625" customWidth="1"/>
     <col min="5" max="5" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="2" t="s">
+    <row r="3" spans="1:5" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2">
+      <c r="A4" s="1">
         <v>1</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="1">
         <v>1.2250000000000001</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="1">
         <v>34.030999999999999</v>
       </c>
       <c r="D4">
